--- a/data/trans_orig/P34B04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,18</t>
+          <t>0,84; 1,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,18</t>
+          <t>0,83; 1,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,59</t>
+          <t>0,92; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,32</t>
+          <t>0,14; 0,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,39</t>
+          <t>0,1; 0,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,68</t>
+          <t>0,48; 0,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,02</t>
+          <t>0,59; 0,99</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,72</t>
+          <t>0,49; 0,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,99</t>
+          <t>0,58; 0,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,27 +807,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,07; 0,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,3</t>
+          <t>0,09; 0,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,42</t>
+          <t>0,29; 0,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,43</t>
+          <t>0,31; 0,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,57</t>
+          <t>0,33; 0,58</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,41</t>
+          <t>0,23; 0,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,7</t>
+          <t>0,43; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,15</t>
+          <t>0,06; 0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,18</t>
+          <t>0,11; 0,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,4</t>
+          <t>0,27; 0,4</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,27</t>
+          <t>0,12; 0,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,24</t>
+          <t>0,1; 0,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,35</t>
+          <t>0,1; 0,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,11</t>
+          <t>0,02; 0,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,14</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,1; 0,22</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,01</t>
+          <t>0,0; 0,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,06</t>
+          <t>0,01; 0,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,0; 0,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,02</t>
+          <t>0,0; 0,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,08</t>
+          <t>0,0; 0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,03</t>
+          <t>0,0; 0,04</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,27</t>
+          <t>0,21; 0,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Edad-trans_orig.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,18</t>
+          <t>0,81; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,57</t>
+          <t>0,96; 1,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,31</t>
+          <t>0,15; 0,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,37</t>
+          <t>0,12; 0,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,68</t>
+          <t>0,49; 0,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,74</t>
+          <t>0,53; 0,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,99</t>
+          <t>0,59; 0,94</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,71</t>
+          <t>0,5; 0,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,74</t>
+          <t>0,49; 0,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,97</t>
+          <t>0,58; 0,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,27 +807,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,18</t>
+          <t>0,08; 0,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,29</t>
+          <t>0,12; 0,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,41</t>
+          <t>0,29; 0,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,45</t>
+          <t>0,3; 0,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,58</t>
+          <t>0,38; 0,6</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -897,32 +897,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,34</t>
+          <t>0,19; 0,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,41</t>
+          <t>0,24; 0,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,69</t>
+          <t>0,42; 0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,09</t>
+          <t>0,01; 0,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,16</t>
+          <t>0,06; 0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,07; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,26</t>
+          <t>0,16; 0,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,4</t>
+          <t>0,25; 0,39</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,27</t>
+          <t>0,12; 0,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,34</t>
+          <t>0,25; 0,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,1</t>
+          <t>0,02; 0,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,12</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,22</t>
+          <t>0,16; 0,25</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1117,22 +1117,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,08</t>
+          <t>0,01; 0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,24</t>
+          <t>0,08; 0,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,21</t>
+          <t>0,1; 0,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,06</t>
+          <t>0,01; 0,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,09</t>
+          <t>0,02; 0,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,05</t>
+          <t>0,01; 0,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,22</t>
+          <t>0,04; 0,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,03</t>
+          <t>0,01; 0,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,05</t>
+          <t>0,02; 0,06</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,47</t>
+          <t>0,38; 0,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,23</t>
+          <t>0,18; 0,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,28</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
     </row>
